--- a/astro-site/public/dl/kit-tareas-pasteleria/13-registro-temperaturas-recepcion.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/13-registro-temperaturas-recepcion.xlsx
@@ -158,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -194,128 +194,11 @@
         <color rgb="009E9E9E"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E0E0E0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E0E0E0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E0E0E0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E0E0E0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -400,16 +283,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -802,14 +675,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="B2:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -817,7 +689,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -873,14 +744,14 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>▸ Hoja Etiquetas de Elaborado: rellena, imprime y pega. Toda elaboración que entre en cámara sale etiquetada.</t>
+          <t>▸ Hoja Etiquetas de Elaborado: rellena, imprime y pega. Toda elaboración que entre en cámara sale etiquetada, y la elaborada con huevo lleva además la HORA (RD 1021/2022, art. 9.3).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>▸ Hoja Vidas Útiles: la referencia de cuánto dura cada elaboración. Es orientativa.</t>
+          <t>▸ Hoja Vidas Útiles: la referencia de cuánto dura cada elaboración. Es orientativa salvo en las filas con huevo: ahí las 24 horas son un tope legal (RD 1021/2022, art. 9.3).</t>
         </is>
       </c>
     </row>
@@ -897,14 +768,14 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>▸ Cámara de refrigeración 0 a 4 °C · cámara de masas 2 a 6 °C · congelador igual o por debajo de −18 °C · vitrinas 2 a 6 °C · abatidor de +65 a +10 °C en menos de 2 horas.</t>
+          <t>▸ Cámara de refrigeración 0 a 4 °C · cámara de masas 2 a 6 °C · congelador igual o por debajo de −18 °C · vitrinas 0 a 4 °C · abatidor de +65 a +10 °C en menos de 2 horas.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>▸ Ajusta los rangos a los de tu plan de APPCC si son distintos: se cambian en Inicio › Formato condicional › Administrar reglas.</t>
+          <t>▸ Ajusta los rangos a los de tu plan de APPCC si son distintos: se cambian en Inicio › Formato condicional › Administrar reglas. Los 4 °C de vitrina no: son el tope que el RD 1021/2022 (art. 4.1, fila 9) fija al producto de pastelería relleno, así que puedes bajarlos, no subirlos.</t>
         </is>
       </c>
     </row>
@@ -932,8 +803,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -951,7 +820,7 @@
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1023,42 +892,42 @@
 (0 a 4 °C)</t>
         </is>
       </c>
-      <c r="C4" s="32" t="n"/>
+      <c r="C4" s="10" t="n"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Cámara de masas
 (2 a 6 °C)</t>
         </is>
       </c>
-      <c r="E4" s="32" t="n"/>
+      <c r="E4" s="10" t="n"/>
       <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Congelador
 (≤ −18 °C)</t>
         </is>
       </c>
-      <c r="G4" s="32" t="n"/>
+      <c r="G4" s="10" t="n"/>
       <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Vitrina 1
-(2 a 6 °C)</t>
-        </is>
-      </c>
-      <c r="I4" s="32" t="n"/>
+(0 a 4 °C)</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="n"/>
       <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Vitrina 2
-(2 a 6 °C)</t>
-        </is>
-      </c>
-      <c r="K4" s="32" t="n"/>
+(0 a 4 °C)</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="n"/>
       <c r="L4" s="9" t="inlineStr">
         <is>
           <t>Abatidor
 (+65 a +10 °C en menos de 2 h)</t>
         </is>
       </c>
-      <c r="M4" s="32" t="n"/>
+      <c r="M4" s="10" t="n"/>
       <c r="N4" s="9" t="inlineStr">
         <is>
           <t>Acción correctiva</t>
@@ -1071,7 +940,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="n"/>
+      <c r="A5" s="10" t="n"/>
       <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Mañana</t>
@@ -1132,8 +1001,8 @@
           <t>Minutos</t>
         </is>
       </c>
-      <c r="N5" s="33" t="n"/>
-      <c r="O5" s="33" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -1740,18 +1609,6 @@
           <t>Número de lecturas anotadas este mes. Toda casilla en rojo exige una acción correctiva escrita.</t>
         </is>
       </c>
-      <c r="D38" s="34" t="n"/>
-      <c r="E38" s="34" t="n"/>
-      <c r="F38" s="34" t="n"/>
-      <c r="G38" s="34" t="n"/>
-      <c r="H38" s="34" t="n"/>
-      <c r="I38" s="34" t="n"/>
-      <c r="J38" s="34" t="n"/>
-      <c r="K38" s="34" t="n"/>
-      <c r="L38" s="34" t="n"/>
-      <c r="M38" s="34" t="n"/>
-      <c r="N38" s="34" t="n"/>
-      <c r="O38" s="32" t="n"/>
     </row>
     <row r="39"/>
     <row r="40" ht="21.8" customHeight="1">
@@ -1760,38 +1617,8 @@
           <t>Qué hacer si una temperatura se sale de rango: comprueba que la puerta cierra y que el equipo no está sobrecargado, traslada el género a otro equipo, anota la acción en esta misma fila y avisa al servicio técnico. Si el producto ha estado fuera de rango más de dos horas, valóralo antes de venderlo y regístralo como merma (→ 10 Plan de Producción Semanal · hoja Producido vs Vendido).</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n"/>
-      <c r="C40" s="35" t="n"/>
-      <c r="D40" s="35" t="n"/>
-      <c r="E40" s="35" t="n"/>
-      <c r="F40" s="35" t="n"/>
-      <c r="G40" s="35" t="n"/>
-      <c r="H40" s="35" t="n"/>
-      <c r="I40" s="35" t="n"/>
-      <c r="J40" s="35" t="n"/>
-      <c r="K40" s="35" t="n"/>
-      <c r="L40" s="35" t="n"/>
-      <c r="M40" s="35" t="n"/>
-      <c r="N40" s="35" t="n"/>
-      <c r="O40" s="36" t="n"/>
-    </row>
-    <row r="41" ht="21.8" customHeight="1">
-      <c r="A41" s="37" t="n"/>
-      <c r="B41" s="38" t="n"/>
-      <c r="C41" s="38" t="n"/>
-      <c r="D41" s="38" t="n"/>
-      <c r="E41" s="38" t="n"/>
-      <c r="F41" s="38" t="n"/>
-      <c r="G41" s="38" t="n"/>
-      <c r="H41" s="38" t="n"/>
-      <c r="I41" s="38" t="n"/>
-      <c r="J41" s="38" t="n"/>
-      <c r="K41" s="38" t="n"/>
-      <c r="L41" s="38" t="n"/>
-      <c r="M41" s="38" t="n"/>
-      <c r="N41" s="38" t="n"/>
-      <c r="O41" s="39" t="n"/>
-    </row>
+    </row>
+    <row r="41" ht="21.8" customHeight="1"/>
     <row r="42"/>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
@@ -1820,9 +1647,9 @@
     <mergeCell ref="C38:O38"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="L4:M4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A43:O43"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="J4:K4"/>
     <mergeCell ref="F4:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:C36">
@@ -1842,12 +1669,12 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:I36">
     <cfRule type="expression" priority="4" dxfId="0">
-      <formula>AND(H6&lt;&gt;"",OR(H6&lt;2,H6&gt;6))</formula>
+      <formula>AND(H6&lt;&gt;"",OR(H6&lt;0,H6&gt;4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:K36">
     <cfRule type="expression" priority="5" dxfId="0">
-      <formula>AND(J6&lt;&gt;"",OR(J6&lt;2,J6&gt;6))</formula>
+      <formula>AND(J6&lt;&gt;"",OR(J6&lt;0,J6&gt;4))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L6:L36">
@@ -2393,16 +2220,16 @@
           <t xml:space="preserve">  Criterios de Rechazo</t>
         </is>
       </c>
-      <c r="B37" s="34" t="n"/>
-      <c r="C37" s="34" t="n"/>
-      <c r="D37" s="34" t="n"/>
-      <c r="E37" s="34" t="n"/>
-      <c r="F37" s="34" t="n"/>
-      <c r="G37" s="34" t="n"/>
-      <c r="H37" s="34" t="n"/>
-      <c r="I37" s="34" t="n"/>
-      <c r="J37" s="34" t="n"/>
-      <c r="K37" s="32" t="n"/>
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="24" t="n"/>
+      <c r="G37" s="24" t="n"/>
+      <c r="H37" s="24" t="n"/>
+      <c r="I37" s="24" t="n"/>
+      <c r="J37" s="24" t="n"/>
+      <c r="K37" s="24" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
@@ -2410,34 +2237,9 @@
           <t>Rechaza la entrega si: el producto refrigerado llega por encima de 4 °C · el congelado presenta signos de descongelación (escarcha, bloque deformado, líquido en la caja) · el envase está roto, abierto o mojado · la fecha de caducidad o de consumo preferente está a menos de 2 días · el vehículo llega sucio o sin frío · el albarán no coincide con lo que recibes. Anota el motivo, haz una foto y avisa al proveedor el mismo día. Aceptado con reserva: la mercancía se recibe, pero la incidencia se anota en el albarán antes de firmarlo y se fotografía; el producto se aparta identificado y no se usa hasta que el proveedor conteste.</t>
         </is>
       </c>
-      <c r="B38" s="35" t="n"/>
-      <c r="C38" s="35" t="n"/>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="35" t="n"/>
-      <c r="G38" s="35" t="n"/>
-      <c r="H38" s="35" t="n"/>
-      <c r="I38" s="35" t="n"/>
-      <c r="J38" s="35" t="n"/>
-      <c r="K38" s="36" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="40" t="n"/>
-      <c r="K39" s="41" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="37" t="n"/>
-      <c r="B40" s="38" t="n"/>
-      <c r="C40" s="38" t="n"/>
-      <c r="D40" s="38" t="n"/>
-      <c r="E40" s="38" t="n"/>
-      <c r="F40" s="38" t="n"/>
-      <c r="G40" s="38" t="n"/>
-      <c r="H40" s="38" t="n"/>
-      <c r="I40" s="38" t="n"/>
-      <c r="J40" s="38" t="n"/>
-      <c r="K40" s="39" t="n"/>
-    </row>
+    </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41"/>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2522,10 +2324,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30.4" customHeight="1">
+    <row r="2" ht="43.6" customHeight="1">
       <c r="B2" s="25" t="inlineStr">
         <is>
-          <t>Toda elaboración que entre en cámara sale etiquetada. Sin etiqueta no hay trazabilidad: ni sabes qué es, ni hasta cuándo sirve. Vidas útiles orientativas en la hoja Vidas Útiles.</t>
+          <t>Toda elaboración que entre en cámara sale etiquetada. Sin etiqueta no hay trazabilidad: ni sabes qué es, ni hasta cuándo sirve. En lo elaborado con huevo la hora es obligatoria (art. 9.3) y el plazo son 24 h desde que se elabora. Vidas útiles en la hoja Vidas Útiles.</t>
         </is>
       </c>
     </row>
@@ -2550,34 +2352,34 @@
     <row r="5" ht="17" customHeight="1">
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="F5" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="F6" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
     </row>
@@ -2636,34 +2438,34 @@
     <row r="11" ht="17" customHeight="1">
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="F11" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
     </row>
@@ -2722,34 +2524,34 @@
     <row r="17" ht="17" customHeight="1">
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="F17" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="F18" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
     </row>
@@ -2808,34 +2610,34 @@
     <row r="23" ht="17" customHeight="1">
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="F23" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
     </row>
@@ -2894,34 +2696,34 @@
     <row r="29" ht="17" customHeight="1">
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="B30" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="F30" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
     </row>
@@ -2980,34 +2782,34 @@
     <row r="35" ht="17" customHeight="1">
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="F35" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="B36" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
     </row>
@@ -3066,34 +2868,34 @@
     <row r="41" ht="17" customHeight="1">
       <c r="B41" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="F41" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="B42" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="D42" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="F42" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
     </row>
@@ -3152,34 +2954,34 @@
     <row r="47" ht="17" customHeight="1">
       <c r="B47" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
       <c r="F47" s="27" t="inlineStr">
         <is>
-          <t>Fecha de elaboración:</t>
+          <t>Fecha y hora de elaboración:</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="B48" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="D48" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
       <c r="F48" s="27" t="inlineStr">
         <is>
-          <t>Fecha límite de consumo:</t>
+          <t>Fecha y hora límite de consumo:</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3091,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1">
+    <row r="5" ht="30.4" customHeight="1">
       <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Crema pastelera</t>
@@ -3302,12 +3104,12 @@
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>48 a 72 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="D5" s="31" t="inlineStr">
         <is>
-          <t>Enfriar en placa fina, nunca en el cazo</t>
+          <t>Con huevo: 24 h de tope (art. 9.3). Enfriar en placa fina, nunca en el cazo</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3157,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1">
+    <row r="8" ht="30.4" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
           <t>Mousse o bavarois</t>
@@ -3368,16 +3170,16 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>3 días</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="D8" s="31" t="inlineStr">
         <is>
-          <t>Montado y sin acabar</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
+          <t>Con huevo: 24 h de tope (art. 9.3). Montado y sin acabar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30.4" customHeight="1">
       <c r="A9" s="28" t="inlineStr">
         <is>
           <t>Merengue italiano</t>
@@ -3390,12 +3192,12 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>3 días</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
         <is>
-          <t>Tapado, sin humedad</t>
+          <t>Con clara: 24 h de tope (art. 9.3). Tapado, sin humedad</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3219,7 @@
       </c>
       <c r="D10" s="31" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="43.6" customHeight="1">
       <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Curd de limón</t>
@@ -3430,12 +3232,12 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>5 a 7 días</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="D11" s="31" t="inlineStr">
         <is>
-          <t>En bote esterilizado</t>
+          <t>Con huevo: 24 h de tope (art. 9.3), salvo estudio que lo acredite estable a temperatura ambiente. En bote esterilizado</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3329,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="30.4" customHeight="1">
       <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Tarta montada con nata</t>
@@ -3540,16 +3342,16 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>24 a 48 h</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="D16" s="31" t="inlineStr">
         <is>
-          <t>Vitrina a 2-6 °C</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
+          <t>Producto relleno: vitrina a 4 °C o menos (art. 4.1, fila 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="43.6" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>Bollería cocida</t>
@@ -3567,7 +3369,7 @@
       </c>
       <c r="D17" s="31" t="inlineStr">
         <is>
-          <t>Al día siguiente, a merma o a promoción</t>
+          <t>Al día siguiente, a merma o a promoción. Si va rellena, a vitrina a 4 °C o menos (art. 4.1, fila 9)</t>
         </is>
       </c>
     </row>
@@ -3618,26 +3420,15 @@
       <c r="D22" s="14" t="n"/>
     </row>
     <row r="23"/>
-    <row r="24">
+    <row r="24" ht="27.7" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
-          <t>Estas vidas útiles son ORIENTATIVAS y suponen elaboración correcta, enfriado rápido, envase limpio y cadena de frío sin cortes. La vida útil de tus elaboraciones la fijas tú y debe constar en tu plan de APPCC; si tienes dudas con una elaboración concreta, consulta con tu asesor en seguridad alimentaria o encarga un estudio de vida útil.</t>
-        </is>
-      </c>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="36" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="40" t="n"/>
-      <c r="D25" s="41" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="37" t="n"/>
-      <c r="B26" s="38" t="n"/>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="39" t="n"/>
-    </row>
+          <t>Las filas que citan el art. 9.3 NO son orientativas: las 24 horas son un TOPE LEGAL para lo elaborado con huevo que no sea estable a temperatura ambiente, y obligan a anotar la fecha y la hora de elaboración. El art. 4.1, fila 9, fija 4 °C o menos al producto de pastelería relleno. En las demás filas la vida útil es ORIENTATIVA y supone elaboración correcta, enfriado rápido, envase limpio y cadena de frío sin cortes: la fijas tú y debe constar en tu plan de APPCC; si tienes dudas con una elaboración concreta, consulta con tu asesor en seguridad alimentaria o encarga un estudio de vida útil. Real Decreto 1021/2022, texto consolidado en https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681 — verificado el 10-09-2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="27.7" customHeight="1"/>
+    <row r="26" ht="27.7" customHeight="1"/>
     <row r="27"/>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">

--- a/astro-site/public/dl/kit-tareas-pasteleria/13-registro-temperaturas-recepcion.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/13-registro-temperaturas-recepcion.xlsx
@@ -158,7 +158,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -194,11 +194,128 @@
         <color rgb="009E9E9E"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E0E0E0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E0E0E0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E0E0E0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -283,6 +400,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -675,13 +802,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B26"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -689,6 +817,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -803,6 +932,8 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -892,42 +1023,42 @@
 (0 a 4 °C)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="n"/>
+      <c r="C4" s="32" t="n"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Cámara de masas
 (2 a 6 °C)</t>
         </is>
       </c>
-      <c r="E4" s="10" t="n"/>
+      <c r="E4" s="32" t="n"/>
       <c r="F4" s="9" t="inlineStr">
         <is>
           <t>Congelador
 (≤ −18 °C)</t>
         </is>
       </c>
-      <c r="G4" s="10" t="n"/>
+      <c r="G4" s="32" t="n"/>
       <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Vitrina 1
 (0 a 4 °C)</t>
         </is>
       </c>
-      <c r="I4" s="10" t="n"/>
+      <c r="I4" s="32" t="n"/>
       <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Vitrina 2
 (0 a 4 °C)</t>
         </is>
       </c>
-      <c r="K4" s="10" t="n"/>
+      <c r="K4" s="32" t="n"/>
       <c r="L4" s="9" t="inlineStr">
         <is>
           <t>Abatidor
 (+65 a +10 °C en menos de 2 h)</t>
         </is>
       </c>
-      <c r="M4" s="10" t="n"/>
+      <c r="M4" s="32" t="n"/>
       <c r="N4" s="9" t="inlineStr">
         <is>
           <t>Acción correctiva</t>
@@ -940,7 +1071,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n"/>
+      <c r="A5" s="33" t="n"/>
       <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Mañana</t>
@@ -1001,8 +1132,8 @@
           <t>Minutos</t>
         </is>
       </c>
-      <c r="N5" s="10" t="n"/>
-      <c r="O5" s="10" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -1609,6 +1740,18 @@
           <t>Número de lecturas anotadas este mes. Toda casilla en rojo exige una acción correctiva escrita.</t>
         </is>
       </c>
+      <c r="D38" s="34" t="n"/>
+      <c r="E38" s="34" t="n"/>
+      <c r="F38" s="34" t="n"/>
+      <c r="G38" s="34" t="n"/>
+      <c r="H38" s="34" t="n"/>
+      <c r="I38" s="34" t="n"/>
+      <c r="J38" s="34" t="n"/>
+      <c r="K38" s="34" t="n"/>
+      <c r="L38" s="34" t="n"/>
+      <c r="M38" s="34" t="n"/>
+      <c r="N38" s="34" t="n"/>
+      <c r="O38" s="32" t="n"/>
     </row>
     <row r="39"/>
     <row r="40" ht="21.8" customHeight="1">
@@ -1617,8 +1760,38 @@
           <t>Qué hacer si una temperatura se sale de rango: comprueba que la puerta cierra y que el equipo no está sobrecargado, traslada el género a otro equipo, anota la acción en esta misma fila y avisa al servicio técnico. Si el producto ha estado fuera de rango más de dos horas, valóralo antes de venderlo y regístralo como merma (→ 10 Plan de Producción Semanal · hoja Producido vs Vendido).</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="21.8" customHeight="1"/>
+      <c r="B40" s="35" t="n"/>
+      <c r="C40" s="35" t="n"/>
+      <c r="D40" s="35" t="n"/>
+      <c r="E40" s="35" t="n"/>
+      <c r="F40" s="35" t="n"/>
+      <c r="G40" s="35" t="n"/>
+      <c r="H40" s="35" t="n"/>
+      <c r="I40" s="35" t="n"/>
+      <c r="J40" s="35" t="n"/>
+      <c r="K40" s="35" t="n"/>
+      <c r="L40" s="35" t="n"/>
+      <c r="M40" s="35" t="n"/>
+      <c r="N40" s="35" t="n"/>
+      <c r="O40" s="36" t="n"/>
+    </row>
+    <row r="41" ht="21.8" customHeight="1">
+      <c r="A41" s="37" t="n"/>
+      <c r="B41" s="38" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="38" t="n"/>
+      <c r="E41" s="38" t="n"/>
+      <c r="F41" s="38" t="n"/>
+      <c r="G41" s="38" t="n"/>
+      <c r="H41" s="38" t="n"/>
+      <c r="I41" s="38" t="n"/>
+      <c r="J41" s="38" t="n"/>
+      <c r="K41" s="38" t="n"/>
+      <c r="L41" s="38" t="n"/>
+      <c r="M41" s="38" t="n"/>
+      <c r="N41" s="38" t="n"/>
+      <c r="O41" s="39" t="n"/>
+    </row>
     <row r="42"/>
     <row r="43">
       <c r="A43" s="20" t="inlineStr">
@@ -1647,9 +1820,9 @@
     <mergeCell ref="C38:O38"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A43:O43"/>
+    <mergeCell ref="A2:O2"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A43:O43"/>
     <mergeCell ref="F4:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:C36">
@@ -2220,16 +2393,16 @@
           <t xml:space="preserve">  Criterios de Rechazo</t>
         </is>
       </c>
-      <c r="B37" s="24" t="n"/>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="24" t="n"/>
-      <c r="E37" s="24" t="n"/>
-      <c r="F37" s="24" t="n"/>
-      <c r="G37" s="24" t="n"/>
-      <c r="H37" s="24" t="n"/>
-      <c r="I37" s="24" t="n"/>
-      <c r="J37" s="24" t="n"/>
-      <c r="K37" s="24" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="34" t="n"/>
+      <c r="D37" s="34" t="n"/>
+      <c r="E37" s="34" t="n"/>
+      <c r="F37" s="34" t="n"/>
+      <c r="G37" s="34" t="n"/>
+      <c r="H37" s="34" t="n"/>
+      <c r="I37" s="34" t="n"/>
+      <c r="J37" s="34" t="n"/>
+      <c r="K37" s="32" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
@@ -2237,9 +2410,34 @@
           <t>Rechaza la entrega si: el producto refrigerado llega por encima de 4 °C · el congelado presenta signos de descongelación (escarcha, bloque deformado, líquido en la caja) · el envase está roto, abierto o mojado · la fecha de caducidad o de consumo preferente está a menos de 2 días · el vehículo llega sucio o sin frío · el albarán no coincide con lo que recibes. Anota el motivo, haz una foto y avisa al proveedor el mismo día. Aceptado con reserva: la mercancía se recibe, pero la incidencia se anota en el albarán antes de firmarlo y se fotografía; el producto se aparta identificado y no se usa hasta que el proveedor conteste.</t>
         </is>
       </c>
-    </row>
-    <row r="39"/>
-    <row r="40"/>
+      <c r="B38" s="35" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="35" t="n"/>
+      <c r="E38" s="35" t="n"/>
+      <c r="F38" s="35" t="n"/>
+      <c r="G38" s="35" t="n"/>
+      <c r="H38" s="35" t="n"/>
+      <c r="I38" s="35" t="n"/>
+      <c r="J38" s="35" t="n"/>
+      <c r="K38" s="36" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="40" t="n"/>
+      <c r="K39" s="41" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="37" t="n"/>
+      <c r="B40" s="38" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="38" t="n"/>
+      <c r="E40" s="38" t="n"/>
+      <c r="F40" s="38" t="n"/>
+      <c r="G40" s="38" t="n"/>
+      <c r="H40" s="38" t="n"/>
+      <c r="I40" s="38" t="n"/>
+      <c r="J40" s="38" t="n"/>
+      <c r="K40" s="39" t="n"/>
+    </row>
     <row r="41"/>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -3426,9 +3624,20 @@
           <t>Las filas que citan el art. 9.3 NO son orientativas: las 24 horas son un TOPE LEGAL para lo elaborado con huevo que no sea estable a temperatura ambiente, y obligan a anotar la fecha y la hora de elaboración. El art. 4.1, fila 9, fija 4 °C o menos al producto de pastelería relleno. En las demás filas la vida útil es ORIENTATIVA y supone elaboración correcta, enfriado rápido, envase limpio y cadena de frío sin cortes: la fijas tú y debe constar en tu plan de APPCC; si tienes dudas con una elaboración concreta, consulta con tu asesor en seguridad alimentaria o encarga un estudio de vida útil. Real Decreto 1021/2022, texto consolidado en https://www.boe.es/buscar/act.php?id=BOE-A-2022-21681 — verificado el 10-09-2026.</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="27.7" customHeight="1"/>
-    <row r="26" ht="27.7" customHeight="1"/>
+      <c r="B24" s="35" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="36" t="n"/>
+    </row>
+    <row r="25" ht="27.7" customHeight="1">
+      <c r="A25" s="40" t="n"/>
+      <c r="D25" s="41" t="n"/>
+    </row>
+    <row r="26" ht="27.7" customHeight="1">
+      <c r="A26" s="37" t="n"/>
+      <c r="B26" s="38" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+    </row>
     <row r="27"/>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
